--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488169_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488169_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3383</v>
+        <v>3.8843</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3715</v>
+        <v>3.6221</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0332</v>
+        <v>0.2623</v>
       </c>
       <c r="G2" t="n">
         <v>2.1411</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.4393</v>
+        <v>-1.8933</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0396</v>
+        <v>-0.789</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.3997</v>
+        <v>-1.1043</v>
       </c>
       <c r="V2" t="n">
         <v>2.8954</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5862</v>
+        <v>2.9599</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0162</v>
+        <v>0.2667</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5701</v>
+        <v>2.6932</v>
       </c>
       <c r="G3" t="n">
         <v>3.1352</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.1501</v>
+        <v>-1.7764</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8754</v>
+        <v>-0.6249</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2746</v>
+        <v>-1.1515</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2518</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2785</v>
+        <v>1.5951</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6958</v>
+        <v>-0.7391</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9744</v>
+        <v>2.3342</v>
       </c>
       <c r="G4" t="n">
         <v>2.4826</v>
@@ -766,13 +766,13 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2335</v>
+        <v>-0.4499</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.332</v>
+        <v>-0.3752</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5655</v>
+        <v>-0.0746</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2523</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3497</v>
+        <v>-0.6429</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9188</v>
+        <v>-1.3105</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.6676</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0857</v>
@@ -922,13 +922,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7185</v>
+        <v>0.4253</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5981</v>
+        <v>0.2064</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1204</v>
+        <v>0.2189</v>
       </c>
       <c r="V6" t="n">
         <v>0.3144</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6079</v>
+        <v>-0.7299</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6254</v>
+        <v>-0.8213</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0175</v>
+        <v>0.0914</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3661</v>
@@ -1000,13 +1000,13 @@
         <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5949</v>
+        <v>-0.7169</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0584</v>
+        <v>-0.2543</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5365</v>
+        <v>-0.4626</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9439</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. ESCAMILLA DE SANTOS</t>
+          <t>I. GARCIA REYES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0563</v>
+        <v>-1.0264</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6989</v>
+        <v>-0.0235</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6425999999999999</v>
+        <v>-1.0029</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.39</v>
+        <v>-0.8337</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6329</v>
+        <v>-0.8107</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0229</v>
+        <v>-0.023</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6501</v>
+        <v>0.0859</v>
       </c>
       <c r="K8" t="n">
-        <v>2.598</v>
+        <v>0.0859</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9479</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0401</v>
+        <v>-0.9196</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0349</v>
+        <v>-0.8966</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.075</v>
+        <v>-0.023</v>
       </c>
       <c r="P8" t="n">
         <v>0.1853</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0382</v>
+        <v>0.1853</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8516</v>
+        <v>-0.378</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4961</v>
+        <v>-0.1094</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3554</v>
+        <v>-0.2686</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. GARCIA REYES</t>
+          <t>D. ESCAMILLA DE SANTOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.155</v>
+        <v>-1.0295</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-1.4915</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0767</v>
+        <v>0.4621</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8337</v>
+        <v>-0.39</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8107</v>
+        <v>2.6329</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.023</v>
+        <v>-3.0229</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0859</v>
+        <v>0.6501</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0859</v>
+        <v>2.598</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.9479</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9196</v>
+        <v>-1.0401</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8966</v>
+        <v>0.0349</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.023</v>
+        <v>-1.075</v>
       </c>
       <c r="P9" t="n">
         <v>0.1853</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1853</v>
+        <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.8248</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1641</v>
+        <v>-0.2888</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3425</v>
+        <v>-0.536</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1929</v>
+        <v>-2.0949</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2716</v>
+        <v>-3.1736</v>
       </c>
       <c r="F10" t="n">
         <v>1.0787</v>
@@ -1234,10 +1234,10 @@
         <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1517</v>
+        <v>-0.0538</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U10" t="n">
         <v>0.06710000000000001</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6265</v>
+        <v>-2.2096</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7569</v>
+        <v>-2.4631</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1304</v>
+        <v>0.2535</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6506999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6614</v>
+        <v>-1.2445</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6019</v>
+        <v>-0.3081</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0595</v>
+        <v>-0.9364</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3144</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9042</v>
+        <v>-3.1854</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7498</v>
+        <v>-1.228</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1544</v>
+        <v>-1.9574</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7668</v>
@@ -1390,13 +1390,13 @@
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1446</v>
+        <v>-1.4257</v>
       </c>
       <c r="T12" t="n">
-        <v>0.102</v>
+        <v>-0.3761</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2465</v>
+        <v>-1.0496</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2518</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.047</v>
+        <v>-3.9491</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9675</v>
+        <v>-2.8696</v>
       </c>
       <c r="F13" t="n">
         <v>-1.0795</v>
@@ -1468,10 +1468,10 @@
         <v>0.1853</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.7191</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6019</v>
+        <v>-0.5039</v>
       </c>
       <c r="U13" t="n">
         <v>-0.2151</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.8037</v>
+        <v>-4.5235</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.2142</v>
+        <v>-2.811</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5895</v>
+        <v>-1.7126</v>
       </c>
       <c r="G14" t="n">
         <v>1.738</v>
@@ -1546,13 +1546,13 @@
         <v>1.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7335</v>
+        <v>-1.4534</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.149</v>
+        <v>-0.7458</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5845</v>
+        <v>-0.7076</v>
       </c>
       <c r="V14" t="n">
         <v>-2.77</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-11.2181</v>
+        <v>-10.6298</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.2674</v>
+        <v>-12.7203</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0495</v>
+        <v>2.090600000000001</v>
       </c>
       <c r="G15" t="n">
         <v>3.604200000000001</v>
@@ -1624,13 +1624,13 @@
         <v>13.8966</v>
       </c>
       <c r="S15" t="n">
-        <v>-11.0987</v>
+        <v>-10.5105</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.8372</v>
+        <v>-4.29</v>
       </c>
       <c r="U15" t="n">
-        <v>-6.261299999999999</v>
+        <v>-6.2203</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9443999999999997</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6934</v>
+        <v>4.3471</v>
       </c>
       <c r="E16" t="n">
-        <v>5.7792</v>
+        <v>0.9116</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0858</v>
+        <v>3.4355</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9696</v>
+        <v>2.6951</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3336</v>
+        <v>0.3435</v>
       </c>
       <c r="I16" t="n">
-        <v>0.636</v>
+        <v>2.3515</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1366</v>
+        <v>1.4184</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8463</v>
+        <v>0.1114</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2903</v>
+        <v>1.307</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.167</v>
+        <v>1.2767</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.5127</v>
+        <v>0.2322</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3457</v>
+        <v>1.0446</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8529</v>
+        <v>-1.297</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>4.9826</v>
+        <v>0.9109</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5516</v>
+        <v>0.7903</v>
       </c>
       <c r="U16" t="n">
-        <v>1.431</v>
+        <v>0.1206</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.538</v>
+        <v>3.3176</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3241</v>
+        <v>0.2343</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2139</v>
+        <v>3.0833</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6951</v>
+        <v>1.2219</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3435</v>
+        <v>-0.2559</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3515</v>
+        <v>1.4778</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4184</v>
+        <v>0.0757</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1114</v>
+        <v>0.0342</v>
       </c>
       <c r="L17" t="n">
-        <v>1.307</v>
+        <v>0.0415</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2767</v>
+        <v>1.1462</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2322</v>
+        <v>-0.2901</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0446</v>
+        <v>1.4363</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.297</v>
+        <v>-0.3706</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0382</v>
+        <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1017</v>
+        <v>0.9246</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2027</v>
+        <v>0.5291</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.101</v>
+        <v>0.3954</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.1259</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3686</v>
+        <v>3.025</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7508</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6178</v>
+        <v>2.4701</v>
       </c>
       <c r="G18" t="n">
         <v>0.2253</v>
@@ -1858,13 +1858,13 @@
         <v>1.297</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5144</v>
+        <v>1.1708</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9103</v>
+        <v>0.7144</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6041</v>
+        <v>0.4564</v>
       </c>
       <c r="V18" t="n">
         <v>1.2583</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.3164</v>
+        <v>2.5116</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4301</v>
+        <v>4.1144</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8863</v>
+        <v>-1.6028</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2219</v>
+        <v>0.9696</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2559</v>
+        <v>0.3336</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4778</v>
+        <v>0.636</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0757</v>
+        <v>3.1366</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0342</v>
+        <v>2.8463</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0415</v>
+        <v>0.2903</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1462</v>
+        <v>-2.167</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2901</v>
+        <v>-2.5127</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4363</v>
+        <v>0.3457</v>
       </c>
       <c r="P19" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.3706</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9235</v>
+        <v>2.8008</v>
       </c>
       <c r="T19" t="n">
-        <v>0.725</v>
+        <v>1.8868</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1985</v>
+        <v>0.914</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1259</v>
+        <v>-1.2589</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1259</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.717</v>
+        <v>1.3997</v>
       </c>
       <c r="E20" t="n">
-        <v>1.97</v>
+        <v>1.4803</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2529</v>
+        <v>-0.0806</v>
       </c>
       <c r="G20" t="n">
         <v>0.6794</v>
@@ -2014,13 +2014,13 @@
         <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0376</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9986</v>
+        <v>0.5089</v>
       </c>
       <c r="U20" t="n">
-        <v>0.039</v>
+        <v>0.2114</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. REYES ALVAREZ</t>
+          <t>J. RICARDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9305</v>
+        <v>0.8858</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2597</v>
+        <v>0.0596</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6708</v>
+        <v>0.8263</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2611</v>
+        <v>0.1152</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-2.8551</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2611</v>
+        <v>2.9703</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.9369</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.6877</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.6246</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2611</v>
+        <v>-1.8217</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-2.1674</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2611</v>
+        <v>0.3457</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1853</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1853</v>
+        <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1696</v>
+        <v>1.0458</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0547</v>
+        <v>0.5696</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2243</v>
+        <v>0.4763</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3144</v>
+        <v>1.7629</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.5041</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PINILLA NUÑEZ</t>
+          <t>A. REYES ALVAREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3221</v>
+        <v>0.8566</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3221</v>
+        <v>0.2597</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.5969</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3221</v>
+        <v>0.2611</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3221</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.2611</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3221</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3221</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.2611</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.2611</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.0958</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.0547</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.1505</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RICARDO</t>
+          <t>J. PINILLA NUÑEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1248</v>
+        <v>0.3221</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3322</v>
+        <v>0.3221</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4569</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1152</v>
+        <v>0.3221</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8551</v>
+        <v>0.3221</v>
       </c>
       <c r="I23" t="n">
-        <v>2.9703</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9369</v>
+        <v>0.3221</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6877</v>
+        <v>0.3221</v>
       </c>
       <c r="L23" t="n">
-        <v>2.6246</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8217</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.1674</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3457</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2848</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1779</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1069</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.7629</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.5041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7121</v>
+        <v>-0.1738</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6632</v>
+        <v>-0.0756</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0489</v>
+        <v>-0.0982</v>
       </c>
       <c r="G24" t="n">
         <v>-3.573</v>
@@ -2326,13 +2326,13 @@
         <v>1.8529</v>
       </c>
       <c r="S24" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.6025</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3867</v>
+        <v>0.2009</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4509</v>
+        <v>0.4016</v>
       </c>
       <c r="V24" t="n">
         <v>0.9439</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.1188</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5432</v>
+        <v>-1.9556</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4244</v>
+        <v>1.449</v>
       </c>
       <c r="G25" t="n">
         <v>1.1948</v>
@@ -2404,13 +2404,13 @@
         <v>1.4823</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4847</v>
+        <v>0.1275</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7113</v>
+        <v>-0.1237</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2266</v>
+        <v>0.2512</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0142</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.2814</v>
+        <v>-1.4493</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.3155</v>
+        <v>-4.4341</v>
       </c>
       <c r="F26" t="n">
-        <v>3.034</v>
+        <v>2.9848</v>
       </c>
       <c r="G26" t="n">
         <v>-5.2553</v>
@@ -2482,13 +2482,13 @@
         <v>2.594</v>
       </c>
       <c r="S26" t="n">
-        <v>1.1548</v>
+        <v>1.9869</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0896</v>
+        <v>0.9709</v>
       </c>
       <c r="U26" t="n">
-        <v>1.0652</v>
+        <v>1.0159</v>
       </c>
       <c r="V26" t="n">
         <v>1.4485</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.6804</v>
+        <v>-3.3178</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.0312</v>
+        <v>-3.5209</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3508</v>
+        <v>0.2031</v>
       </c>
       <c r="G27" t="n">
         <v>-2.4607</v>
@@ -2560,13 +2560,13 @@
         <v>1.1117</v>
       </c>
       <c r="S27" t="n">
-        <v>1.3502</v>
+        <v>0.7129</v>
       </c>
       <c r="T27" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.2689</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5917</v>
+        <v>0.4439</v>
       </c>
       <c r="V27" t="n">
         <v>-1.3847</v>
@@ -2593,22 +2593,22 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>11.2181</v>
+        <v>11.218</v>
       </c>
       <c r="E28" t="n">
         <v>-2.049300000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>13.2673</v>
+        <v>13.2674</v>
       </c>
       <c r="G28" t="n">
-        <v>-3.604499999999999</v>
+        <v>-3.6045</v>
       </c>
       <c r="H28" t="n">
         <v>-13.4343</v>
       </c>
       <c r="I28" t="n">
-        <v>9.829800000000001</v>
+        <v>9.829799999999999</v>
       </c>
       <c r="J28" t="n">
         <v>0.2376999999999994</v>
@@ -2626,7 +2626,7 @@
         <v>-10.7933</v>
       </c>
       <c r="O28" t="n">
-        <v>6.951499999999999</v>
+        <v>6.9515</v>
       </c>
       <c r="P28" t="n">
         <v>2.779300000000001</v>
@@ -2638,10 +2638,10 @@
         <v>16.6759</v>
       </c>
       <c r="S28" t="n">
-        <v>11.0987</v>
+        <v>11.0988</v>
       </c>
       <c r="T28" t="n">
-        <v>6.2616</v>
+        <v>6.2614</v>
       </c>
       <c r="U28" t="n">
         <v>4.8372</v>
